--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484533_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484533_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>J. LE BERRE CASTILLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.254</v>
+        <v>3.1125</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8602</v>
+        <v>3.258</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6062</v>
+        <v>-0.1455</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.134</v>
+        <v>1.5584</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6194</v>
+        <v>-1.1759</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7533</v>
+        <v>2.7343</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6905</v>
+        <v>2.9172</v>
       </c>
       <c r="K2" t="n">
-        <v>2.155</v>
+        <v>-0.4584</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4645</v>
+        <v>3.3756</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8244</v>
+        <v>-1.3588</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5356</v>
+        <v>-0.7175</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2888</v>
+        <v>-0.6413</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4717</v>
+        <v>0.3709</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7195</v>
+        <v>-0.1485</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2478</v>
+        <v>0.5194</v>
       </c>
       <c r="V2" t="n">
         <v>0.6335</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6335</v>
+        <v>1.5889</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LE BERRE CASTILLO</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3515</v>
+        <v>2.6919</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3236</v>
+        <v>2.7575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0279</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5584</v>
+        <v>0.6491</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1759</v>
+        <v>0.0558</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7343</v>
+        <v>0.5933</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9172</v>
+        <v>2.5437</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4584</v>
+        <v>1.1487</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3756</v>
+        <v>1.3949</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3588</v>
+        <v>-1.8946</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7175</v>
+        <v>-1.0929</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6413</v>
+        <v>-0.8017</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R3" t="n">
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3901</v>
+        <v>0.5767</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0829</v>
+        <v>0.3971</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6928</v>
+        <v>0.1797</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9548</v>
+        <v>2.4279</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1938</v>
+        <v>2.8854</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.239</v>
+        <v>-0.4576</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6491</v>
+        <v>-0.134</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0558</v>
+        <v>0.6194</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5933</v>
+        <v>-0.7533</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5437</v>
+        <v>1.6905</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1487</v>
+        <v>2.155</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3949</v>
+        <v>-0.4645</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8946</v>
+        <v>-1.8244</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0929</v>
+        <v>-1.5356</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8017</v>
+        <v>-0.2888</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.1833</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1604</v>
+        <v>0.6456</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1666</v>
+        <v>0.7447</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0063</v>
+        <v>-0.0992</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1306</v>
+        <v>0.1141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5182</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6489</v>
+        <v>-0.5002</v>
       </c>
       <c r="G6" t="n">
         <v>0.1187</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2493</v>
+        <v>-0.0045</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0259</v>
+        <v>0.1746</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3828</v>
+        <v>-0.8636</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4806</v>
+        <v>0.9998</v>
       </c>
       <c r="F7" t="n">
         <v>-1.8634</v>
@@ -1000,10 +1000,10 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6041</v>
+        <v>0.1233</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3643</v>
+        <v>-0.1165</v>
       </c>
       <c r="U7" t="n">
         <v>0.2398</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4412</v>
+        <v>-1.0016</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8452</v>
+        <v>1.2849</v>
       </c>
       <c r="F8" t="n">
         <v>-2.2865</v>
@@ -1078,10 +1078,10 @@
         <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9344</v>
+        <v>-0.4947</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9728</v>
+        <v>-0.5332</v>
       </c>
       <c r="U8" t="n">
         <v>0.0384</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.802</v>
+        <v>-1.8591</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1102</v>
+        <v>-1.2169</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6917</v>
+        <v>-0.6422</v>
       </c>
       <c r="G9" t="n">
         <v>0.8408</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3154</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8627</v>
+        <v>0.0306</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5473</v>
+        <v>0.5969</v>
       </c>
       <c r="V9" t="n">
         <v>-0.945</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3286</v>
+        <v>-2.7814</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7354</v>
+        <v>-1.3368</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5932</v>
+        <v>-1.4446</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5477</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8541</v>
+        <v>-0.3069</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4223</v>
+        <v>-0.0237</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4318</v>
+        <v>-0.2832</v>
       </c>
       <c r="V10" t="n">
         <v>0.6231</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.599</v>
+        <v>-5.5477</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5721</v>
+        <v>-4.7776</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0269</v>
+        <v>-0.7701</v>
       </c>
       <c r="G11" t="n">
         <v>-10.068</v>
@@ -1312,13 +1312,13 @@
         <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1629</v>
+        <v>1.2142</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3447</v>
+        <v>0.1392</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8182</v>
+        <v>1.075</v>
       </c>
       <c r="V11" t="n">
         <v>3.4894</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7751</v>
+        <v>-5.8158</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9822</v>
+        <v>-2.2707</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7929</v>
+        <v>-3.5452</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1854</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4223</v>
+        <v>-0.463</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0536</v>
+        <v>-0.2349</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4759</v>
+        <v>-0.2281</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5339</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.9985</v>
+        <v>-7.622300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.722200000000001</v>
+        <v>4.0985</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.7208</v>
+        <v>-11.7209</v>
       </c>
       <c r="G13" t="n">
         <v>-10.9057</v>
@@ -1468,13 +1468,13 @@
         <v>10.0792</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9127</v>
+        <v>2.2891</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3005</v>
+        <v>0.07570000000000005</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2132</v>
+        <v>2.2133</v>
       </c>
       <c r="V13" t="n">
         <v>1.911</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5966</v>
+        <v>5.706</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7168</v>
+        <v>5.5245</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1202</v>
+        <v>0.1814</v>
       </c>
       <c r="G14" t="n">
         <v>6.8635</v>
@@ -1546,13 +1546,13 @@
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6725</v>
+        <v>-0.5632</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6802</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0077</v>
+        <v>0.3094</v>
       </c>
       <c r="V14" t="n">
         <v>0.3219</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8828</v>
+        <v>3.1597</v>
       </c>
       <c r="E15" t="n">
         <v>2.701</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1819</v>
+        <v>0.4587</v>
       </c>
       <c r="G15" t="n">
         <v>2.2703</v>
@@ -1624,13 +1624,13 @@
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0472</v>
+        <v>0.2296</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U15" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6231</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4841</v>
+        <v>2.6925</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0548</v>
+        <v>2.8624</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5707</v>
+        <v>-0.17</v>
       </c>
       <c r="G16" t="n">
         <v>0.7979000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.5498</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1305</v>
+        <v>0.0779</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1456</v>
+        <v>-0.0467</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2761</v>
+        <v>0.1246</v>
       </c>
       <c r="V16" t="n">
         <v>1.267</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7759</v>
+        <v>2.0491</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7104</v>
+        <v>2.5746</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0654</v>
+        <v>-0.5255</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1549</v>
+        <v>4.4019</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7927</v>
+        <v>0.8758</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6378</v>
+        <v>3.5261</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2511</v>
+        <v>4.1884</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5169</v>
+        <v>1.4955</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7342</v>
+        <v>2.6929</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.406</v>
+        <v>0.2134</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3097</v>
+        <v>-0.6198</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0964</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
         <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0303</v>
+        <v>0.197</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1086</v>
+        <v>0.2187</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9217</v>
+        <v>-0.0217</v>
       </c>
       <c r="V17" t="n">
-        <v>1.267</v>
+        <v>-1.267</v>
       </c>
       <c r="W17" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7475</v>
+        <v>1.6068</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5746</v>
+        <v>1.7104</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.1036</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4019</v>
+        <v>-0.1549</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8758</v>
+        <v>-0.7927</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5261</v>
+        <v>0.6378</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1884</v>
+        <v>1.2511</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4955</v>
+        <v>0.5169</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6929</v>
+        <v>0.7342</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2134</v>
+        <v>-1.406</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6198</v>
+        <v>-1.3097</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.0964</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
         <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1046</v>
+        <v>0.8612</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2187</v>
+        <v>0.1086</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3233</v>
+        <v>0.7526</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.267</v>
+        <v>1.267</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1239</v>
+        <v>1.4649</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8508</v>
+        <v>1.0431</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2731</v>
+        <v>0.4218</v>
       </c>
       <c r="G19" t="n">
         <v>1.0618</v>
@@ -1936,13 +1936,13 @@
         <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3044</v>
+        <v>0.0366</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0291</v>
+        <v>0.1195</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.409</v>
+        <v>0.3251</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0366</v>
+        <v>0.3251</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3724</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4379</v>
+        <v>0.3251</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1646</v>
+        <v>0.3251</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6025</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1844</v>
+        <v>0.3251</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4026</v>
+        <v>0.3251</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2182</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6223</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3843</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.118</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1297</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0117</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3251</v>
+        <v>0.2211</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3251</v>
+        <v>-0.1557</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.3768</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3251</v>
+        <v>0.4379</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3251</v>
+        <v>-0.1646</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.6025</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3251</v>
+        <v>-0.1844</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3251</v>
+        <v>-0.4026</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.2182</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.6223</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.3843</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.306</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.322</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1667</v>
+        <v>-0.1758</v>
       </c>
       <c r="E22" t="n">
         <v>0.2557</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.089</v>
+        <v>-0.4315</v>
       </c>
       <c r="G22" t="n">
         <v>0.3265</v>
@@ -2170,13 +2170,13 @@
         <v>1.6493</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3845</v>
+        <v>0.042</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4419</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8264</v>
+        <v>0.4839</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2774</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8485</v>
+        <v>-0.898</v>
       </c>
       <c r="E23" t="n">
         <v>-0.0801</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7683</v>
+        <v>-0.8179</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7973</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0511</v>
+        <v>-0.1007</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U23" t="n">
-        <v>0.114</v>
+        <v>0.0645</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5816</v>
+        <v>-2.3325</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6151</v>
+        <v>-0.519</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9665</v>
+        <v>-1.8135</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2216</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0197</v>
+        <v>0.2294</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3869</v>
+        <v>-0.2907</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3672</v>
+        <v>0.5201</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2566</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.083</v>
+        <v>-3.5382</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8096</v>
+        <v>-4.5212</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7266</v>
+        <v>0.983</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4053</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8793</v>
+        <v>-0.3345</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5505</v>
+        <v>-0.2621</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3288</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0.3011</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.998499999999998</v>
+        <v>10.2807</v>
       </c>
       <c r="E26" t="n">
-        <v>11.721</v>
+        <v>11.7208</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.7224</v>
+        <v>-1.4403</v>
       </c>
       <c r="G26" t="n">
         <v>10.9058</v>
       </c>
       <c r="H26" t="n">
-        <v>4.335000000000001</v>
+        <v>4.335</v>
       </c>
       <c r="I26" t="n">
         <v>6.570799999999999</v>
@@ -2467,7 +2467,7 @@
         <v>-8.330399999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.2437</v>
+        <v>-6.243699999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-2.0869</v>
@@ -2482,13 +2482,13 @@
         <v>10.9955</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9125000000000001</v>
+        <v>0.3693</v>
       </c>
       <c r="T26" t="n">
         <v>-2.2133</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3007</v>
+        <v>2.5827</v>
       </c>
       <c r="V26" t="n">
         <v>-1.911</v>
